--- a/docs/03_test/ホワイトボックステスト.xlsx
+++ b/docs/03_test/ホワイトボックステスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD67227F-6C9E-4D4B-A8B9-1136CFC11938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F3D776-7B70-4F0E-AAEB-8743BD571147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2055" windowWidth="29040" windowHeight="15720" xr2:uid="{9A50F9FF-CD5D-423C-A42E-F2DF85B5A59E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9A50F9FF-CD5D-423C-A42E-F2DF85B5A59E}"/>
   </bookViews>
   <sheets>
     <sheet name="リポジトリのテストケース" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="53">
   <si>
     <t>Department</t>
     <phoneticPr fontId="1"/>
@@ -274,6 +274,51 @@
   </si>
   <si>
     <t>Employee_FindAll_ReturnsZeroDepartment</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リポジトリのホワイトボックステスト　須崎千穂子</t>
+    <rPh sb="18" eb="20">
+      <t>スザキ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>チホコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事前条件</t>
+    <rPh sb="0" eb="2">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>postgresデータベースに接続できる。</t>
+    <rPh sb="15" eb="17">
+      <t>セツゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト判定</t>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>○</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -344,7 +389,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -364,6 +409,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -387,23 +438,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>571499</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>40821</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>9068</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>45356</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>171524</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>574295</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1387927</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>16326</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F0F8659-C73B-1AD8-7F73-63C73E658DE3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{540FDEE8-193B-E934-2FAE-C05AEC01D6BC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -419,8 +470,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14927035" y="272142"/>
-          <a:ext cx="13536914" cy="533474"/>
+          <a:off x="9068" y="9996713"/>
+          <a:ext cx="3728359" cy="2012042"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -431,23 +482,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>208643</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>358465</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>230316</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>4598828</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>22357</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{540FDEE8-193B-E934-2FAE-C05AEC01D6BC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFFFD5E6-8B5B-DA73-C92A-3303BEE76C25}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -463,8 +514,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15008679" y="966107"/>
-          <a:ext cx="4277322" cy="2543530"/>
+          <a:off x="0" y="8572500"/>
+          <a:ext cx="13643042" cy="947643"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -475,23 +526,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>199185</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>31429</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>4653643</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>10675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFFFD5E6-8B5B-DA73-C92A-3303BEE76C25}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00F557C2-AF32-9124-0CDE-A5BFB3E7D695}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -499,16 +550,17 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
+      <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:srcRect l="400"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15008679" y="3973286"/>
-          <a:ext cx="13479756" cy="943107"/>
+          <a:off x="0" y="6858000"/>
+          <a:ext cx="13697857" cy="1743318"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -817,7 +869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A560D93-453A-4494-BB7A-83F70050B738}">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="13.5" customWidth="1"/>
@@ -825,110 +877,72 @@
     <col min="5" max="5" width="16.08203125" customWidth="1"/>
     <col min="6" max="6" width="44.1640625" customWidth="1"/>
     <col min="7" max="7" width="69.75" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="17" max="17" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
+    <row r="1" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B4" t="s">
         <v>20</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E4" t="s">
         <v>44</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F4" t="s">
         <v>24</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="5">
+      <c r="H4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="5">
         <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="5">
-        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>2</v>
@@ -937,44 +951,56 @@
         <v>5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+        <v>25</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="8">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>3</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
       </c>
+      <c r="H6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="8">
+        <v>46168</v>
+      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>4</v>
@@ -983,160 +1009,201 @@
         <v>7</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="H7" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="8">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="H8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="8">
+        <v>46168</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>27</v>
+        <v>9</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="H9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="8">
+        <v>46168</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="H10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="8">
+        <v>46168</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
         <v>0</v>
       </c>
       <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11" s="8">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="5">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" s="8">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="5">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="D13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q12" s="6"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>46</v>
+      <c r="F13" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="H13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="8">
+        <v>46168</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" s="5">
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>4</v>
@@ -1145,21 +1212,27 @@
         <v>7</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="H14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="8">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>2</v>
@@ -1168,44 +1241,57 @@
         <v>5</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" t="s">
-        <v>14</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="8">
+        <v>46168</v>
+      </c>
+      <c r="Q15" s="6"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>35</v>
+        <v>3</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="G16" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H16" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="8">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>4</v>
@@ -1214,105 +1300,226 @@
         <v>7</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H17" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" s="8">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>14</v>
+      </c>
+      <c r="H18" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="8">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>37</v>
+        <v>9</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="G19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>12</v>
+      </c>
+      <c r="H19" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="8">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" s="8">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21">
         <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21">
-        <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
       </c>
       <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="8">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22">
         <v>18</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" s="8">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" s="8">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G24" t="s">
         <v>13</v>
       </c>
+      <c r="H24" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" s="8">
+        <v>46168</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/docs/03_test/ホワイトボックステスト.xlsx
+++ b/docs/03_test/ホワイトボックステスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F3D776-7B70-4F0E-AAEB-8743BD571147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FDC199-1DF5-4E31-8D08-7E71FFC2AF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9A50F9FF-CD5D-423C-A42E-F2DF85B5A59E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="61">
   <si>
     <t>Department</t>
     <phoneticPr fontId="1"/>
@@ -221,9 +221,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Department_Delete_Exception</t>
-  </si>
-  <si>
     <t>Employee_FindAll_Exception</t>
   </si>
   <si>
@@ -319,6 +316,54 @@
   </si>
   <si>
     <t>○</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Department_Renewal_Success</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Department_Delete_Exception</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Department_Renewal_Exception</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Renewal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正しく更新できたとき</t>
+    <rPh sb="0" eb="1">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Employee_Renewal_Success</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Employee_Renewal_Exception</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正しく更新できたとき(Department=null)</t>
+    <rPh sb="0" eb="1">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Employee_Renewal_Success_Department_null</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -411,11 +456,11 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -438,23 +483,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>9068</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>45356</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1387927</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>16326</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2144594</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>91794</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{540FDEE8-193B-E934-2FAE-C05AEC01D6BC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8C50DFC-10DA-07E0-7FD8-4ECA4AB61774}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -470,8 +515,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9068" y="9996713"/>
-          <a:ext cx="3728359" cy="2012042"/>
+          <a:off x="653143" y="7796893"/>
+          <a:ext cx="10526594" cy="4486901"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -482,23 +527,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>208643</xdr:rowOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>4598828</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>22357</xdr:rowOff>
+      <xdr:colOff>2268436</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>120373</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="6" name="図 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFFFD5E6-8B5B-DA73-C92A-3303BEE76C25}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94DD3EB4-81AA-EDF9-FE60-F8868FCC09C1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -514,53 +559,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="8572500"/>
-          <a:ext cx="13643042" cy="947643"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>81643</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>4653643</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>10675</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00F557C2-AF32-9124-0CDE-A5BFB3E7D695}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:srcRect l="400"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="6858000"/>
-          <a:ext cx="13697857" cy="1743318"/>
+          <a:off x="653143" y="12654643"/>
+          <a:ext cx="10650436" cy="4515480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -869,7 +869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A560D93-453A-4494-BB7A-83F70050B738}">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="13.5" customWidth="1"/>
@@ -881,31 +881,31 @@
     <col min="17" max="17" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
+      <c r="B2" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -916,10 +916,10 @@
         <v>21</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>43</v>
-      </c>
-      <c r="E4" t="s">
-        <v>44</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
@@ -928,13 +928,13 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" t="s">
         <v>50</v>
       </c>
-      <c r="I4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="5" spans="1:9" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -957,13 +957,13 @@
         <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+        <v>51</v>
+      </c>
+      <c r="I5" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5">
         <v>2</v>
       </c>
@@ -980,19 +980,19 @@
         <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>52</v>
-      </c>
-      <c r="I6" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+        <v>51</v>
+      </c>
+      <c r="I6" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -1015,13 +1015,13 @@
         <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+        <v>51</v>
+      </c>
+      <c r="I7" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5">
         <v>4</v>
       </c>
@@ -1044,13 +1044,13 @@
         <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I8" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+        <v>51</v>
+      </c>
+      <c r="I8" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5">
         <v>5</v>
       </c>
@@ -1073,13 +1073,13 @@
         <v>12</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+        <v>51</v>
+      </c>
+      <c r="I9" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5">
         <v>6</v>
       </c>
@@ -1102,13 +1102,13 @@
         <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+        <v>51</v>
+      </c>
+      <c r="I10" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5">
         <v>7</v>
       </c>
@@ -1131,13 +1131,13 @@
         <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>52</v>
-      </c>
-      <c r="I11" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+        <v>51</v>
+      </c>
+      <c r="I11" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5">
         <v>8</v>
       </c>
@@ -1160,13 +1160,13 @@
         <v>13</v>
       </c>
       <c r="H12" t="s">
-        <v>52</v>
-      </c>
-      <c r="I12" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+        <v>51</v>
+      </c>
+      <c r="I12" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5">
         <v>9</v>
       </c>
@@ -1183,19 +1183,19 @@
         <v>5</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
         <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I13" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+        <v>51</v>
+      </c>
+      <c r="I13" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5">
         <v>10</v>
       </c>
@@ -1212,79 +1212,78 @@
         <v>7</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
       </c>
       <c r="H14" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15">
+        <v>51</v>
+      </c>
+      <c r="I14" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="5">
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>11</v>
+        <v>52</v>
+      </c>
+      <c r="G15" t="s">
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>52</v>
-      </c>
-      <c r="I15" s="8">
-        <v>46168</v>
-      </c>
-      <c r="Q15" s="6"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16">
+        <v>51</v>
+      </c>
+      <c r="I15" s="7">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="5">
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>46</v>
+        <v>4</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H16" t="s">
-        <v>52</v>
-      </c>
-      <c r="I16" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17">
+        <v>51</v>
+      </c>
+      <c r="I16" s="7">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="5">
         <v>13</v>
       </c>
       <c r="B17" t="s">
@@ -1294,84 +1293,85 @@
         <v>1</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" t="s">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="H17" t="s">
-        <v>52</v>
-      </c>
-      <c r="I17" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18">
+        <v>51</v>
+      </c>
+      <c r="I17" s="7">
+        <v>46168</v>
+      </c>
+      <c r="Q17" s="6"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="5">
         <v>14</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>34</v>
+        <v>3</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H18" t="s">
-        <v>52</v>
-      </c>
-      <c r="I18" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19">
+        <v>51</v>
+      </c>
+      <c r="I18" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="5">
         <v>15</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H19" t="s">
-        <v>52</v>
-      </c>
-      <c r="I19" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20">
+        <v>51</v>
+      </c>
+      <c r="I19" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="5">
         <v>16</v>
       </c>
       <c r="B20" t="s">
@@ -1381,62 +1381,62 @@
         <v>8</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>2</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>52</v>
-      </c>
-      <c r="I20" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21">
+        <v>51</v>
+      </c>
+      <c r="I20" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="5">
         <v>17</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G21" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H21" t="s">
-        <v>52</v>
-      </c>
-      <c r="I21" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22">
+        <v>51</v>
+      </c>
+      <c r="I21" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="5">
         <v>18</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>4</v>
@@ -1445,56 +1445,56 @@
         <v>7</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22" t="s">
-        <v>52</v>
-      </c>
-      <c r="I22" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23">
+        <v>51</v>
+      </c>
+      <c r="I22" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="5">
         <v>19</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G23" t="s">
         <v>17</v>
       </c>
       <c r="H23" t="s">
-        <v>52</v>
-      </c>
-      <c r="I23" s="8">
-        <v>46168</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24">
+        <v>51</v>
+      </c>
+      <c r="I23" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="5">
         <v>20</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>4</v>
@@ -1503,16 +1503,161 @@
         <v>7</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24" t="s">
-        <v>52</v>
-      </c>
-      <c r="I24" s="8">
-        <v>46168</v>
+        <v>51</v>
+      </c>
+      <c r="I24" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="5">
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I25" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="5">
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s">
+        <v>51</v>
+      </c>
+      <c r="I26" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="5">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G27" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" t="s">
+        <v>51</v>
+      </c>
+      <c r="I27" s="7">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="5">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" t="s">
+        <v>51</v>
+      </c>
+      <c r="I28" s="7">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="5">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>51</v>
+      </c>
+      <c r="I29" s="7">
+        <v>46169</v>
       </c>
     </row>
   </sheetData>
